--- a/pages/shp/uploads/11-09-2026 - 11-09-2026.xlsx
+++ b/pages/shp/uploads/11-09-2026 - 11-09-2026.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="395">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -347,40 +347,130 @@
     <t>FLAG PROPORSIONAL NETTO</t>
   </si>
   <si>
-    <t>000261NIW34520260911000649</t>
-  </si>
-  <si>
-    <t>261</t>
+    <t>000030NIW34520260911001417</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>050100</t>
   </si>
   <si>
     <t>050500</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>LK</t>
+  </si>
+  <si>
+    <t>082570</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>0003</t>
+  </si>
+  <si>
+    <t>02080000</t>
+  </si>
+  <si>
+    <t>IDCGK</t>
+  </si>
+  <si>
+    <t>LKCMB</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
+    <t>DN</t>
+  </si>
+  <si>
     <t>BANDUNG</t>
   </si>
   <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
     <t>YUS YULIUS</t>
   </si>
   <si>
-    <t>EXIM MANAGER</t>
-  </si>
-  <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>020554</t>
-  </si>
-  <si>
-    <t>000261NIW34520260911000648</t>
-  </si>
-  <si>
-    <t>020550</t>
+    <t>MANAGER EXIM</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>462999</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>000030NIW34520260911001416</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>07440000</t>
+  </si>
+  <si>
+    <t>CNSZX</t>
+  </si>
+  <si>
+    <t>462658</t>
+  </si>
+  <si>
+    <t>000030NIW34520260911001414</t>
+  </si>
+  <si>
+    <t>040300</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>IDTPP</t>
+  </si>
+  <si>
+    <t>USW5A</t>
+  </si>
+  <si>
+    <t>575629</t>
+  </si>
+  <si>
+    <t>000030NIW34520260911001415</t>
+  </si>
+  <si>
+    <t>USCVG</t>
+  </si>
+  <si>
+    <t>EXW</t>
+  </si>
+  <si>
+    <t>576459</t>
   </si>
   <si>
     <t>KODE FASILITAS TARIF</t>
@@ -395,196 +485,233 @@
     <t>NPWP BILLING</t>
   </si>
   <si>
+    <t>SERI</t>
+  </si>
+  <si>
+    <t>KODE ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS IDENTITAS</t>
+  </si>
+  <si>
+    <t>NOMOR IDENTITAS</t>
+  </si>
+  <si>
+    <t>NAMA ENTITAS</t>
+  </si>
+  <si>
+    <t>ALAMAT ENTITAS</t>
+  </si>
+  <si>
+    <t>NIB ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS API</t>
+  </si>
+  <si>
+    <t>KODE STATUS</t>
+  </si>
+  <si>
+    <t>NOMOR IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>TANGGAL IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE NEGARA</t>
+  </si>
+  <si>
+    <t>NIPER ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI KONSOLIDATOR</t>
+  </si>
+  <si>
+    <t>KODE AFILIASI</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>0013107743062000000000</t>
+  </si>
+  <si>
+    <t>BIROTIKA SEMESTA</t>
+  </si>
+  <si>
+    <t>MULIA BUSINESS PARK BLD F, JL MT. HARYONO KAV 58-60 RT.000 RW.000, PANCORAN, PANCORAN, KOTA ADMINISTRASI JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
+    <t>TEEJAY LANKA</t>
+  </si>
+  <si>
+    <t>BLOCK D8-D14, SEETHAWAKA, E.P.Z
+107000 AVISSAWELLA WESTERN PROVINCE
+ATTN : HIMASHA HARRISON/ROSHAN</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>PPH</t>
-  </si>
-  <si>
-    <t>BMTP</t>
-  </si>
-  <si>
-    <t>PPN</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>SERI</t>
-  </si>
-  <si>
-    <t>KODE ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS IDENTITAS</t>
-  </si>
-  <si>
-    <t>NOMOR IDENTITAS</t>
-  </si>
-  <si>
-    <t>NAMA ENTITAS</t>
-  </si>
-  <si>
-    <t>ALAMAT ENTITAS</t>
-  </si>
-  <si>
-    <t>NIB ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS API</t>
-  </si>
-  <si>
-    <t>KODE STATUS</t>
-  </si>
-  <si>
-    <t>NOMOR IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>TANGGAL IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE NEGARA</t>
-  </si>
-  <si>
-    <t>NIPER ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI KONSOLIDATOR</t>
-  </si>
-  <si>
-    <t>KODE AFILIASI</t>
+    <t>0745406926444000000000</t>
+  </si>
+  <si>
+    <t>NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0220103231143</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0745406926444000000000</t>
-  </si>
-  <si>
-    <t>NIRWANA ALABARE GARMENT</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
+    <t>13</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>TOP FORM BRASSIERE MFG. CO., LIMITED (SHENZHEN OFFICE)</t>
+  </si>
+  <si>
+    <t>6/F, BLOCK 19, PHASE 2
+LIAN CHUANG TECHNOLOGY PARK, 23 BU LAN ROAD
+NAN WAN, LONG GANG DISTRICT, 518112 SHENZHEN
+ATTN : IRIS ZHANG</t>
+  </si>
+  <si>
+    <t>0926856451045000000000</t>
+  </si>
+  <si>
+    <t>KBN PRIMA LOGISTIK</t>
+  </si>
+  <si>
+    <t>GEDUNG MAWAR, JALAN RAYA CAKUNG CILINCING, TANJUNG PRIOK RT.000 RW.000, SUKAPURA, CILINCING, KOTA ADMINISTRASI JAKARTA UTARA, DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>000000000000000</t>
+  </si>
+  <si>
+    <t>(FAR EASTERN)FU KWOK KNITTING &amp; GARMENT CO., LTD</t>
+  </si>
+  <si>
+    <t>110, NEI-HUAN SOUTH ROAD, NANZIH DIST, KAOHSIUNG , 811 TAIWAN</t>
+  </si>
+  <si>
+    <t>I AM BEYOND, LLC</t>
+  </si>
+  <si>
+    <t>11248 PLAYA COURT SUITE A, CULVER CITY, 
+CA 90230, UNITED STATES</t>
+  </si>
+  <si>
+    <t>110, NEI-HUAN SOUTH ROAD, NANZIH DIST, KAOHSIUNG , 811 TAIWAN
+PHONE NO: 886 73611989
+EMAIL ADDRESS: EMILY@FUKWOK.COM.TW</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>WARRIOR INTL TRADING LIMITED C/O</t>
+  </si>
+  <si>
+    <t>IMAGE SOLUTIONS APPAREL INC 
+2931 REDONDO AVE LONG BEACH
+CA 908062445 USA</t>
+  </si>
+  <si>
+    <t>IMAGE SOLUTIONS APPAREL INC</t>
+  </si>
+  <si>
+    <t>2931 REDONDO AVE LONG BEACH,CA 908062445 USA</t>
+  </si>
+  <si>
+    <t>NOMOR DOKUMEN</t>
+  </si>
+  <si>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS</t>
+  </si>
+  <si>
+    <t>KODE IJIN</t>
+  </si>
+  <si>
+    <t>920</t>
   </si>
   <si>
     <t>16/MK/WBC.09/2026</t>
   </si>
   <si>
-    <t>01-20-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>1000000004846125000000</t>
-  </si>
-  <si>
-    <t>ARISE EMBROIDERY INDONESIA</t>
-  </si>
-  <si>
-    <t>JALAN BUYUT (KP KUTASIRIP) RT.003 RW.014, PEGAMBIRAN, LEMAHWUNGKUK, KOTA CIREBON, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>0316593664439000000000</t>
-  </si>
-  <si>
-    <t>HANDSOMEKOVI INDONESIA</t>
-  </si>
-  <si>
-    <t>DSN SIDAMUKTI RT 022 RW 012 RT.000 RW.000, WANAKERTA, PURWADADI, KABUPATEN SUBANG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>NOMOR DOKUMEN</t>
-  </si>
-  <si>
-    <t>TANGGAL DOKUMEN</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS</t>
-  </si>
-  <si>
-    <t>KODE IJIN</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>3495/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>236/NAG/KK/VIII/2026</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>CBD 2026 08 898 01 26037</t>
-  </si>
-  <si>
-    <t>994</t>
-  </si>
-  <si>
-    <t>002955/BPJ/CB/2026</t>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>0219/E/NAK/0926</t>
   </si>
   <si>
     <t>217</t>
   </si>
   <si>
-    <t>41, 42, 43</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>029808</t>
-  </si>
-  <si>
-    <t>2026-07-28</t>
-  </si>
-  <si>
-    <t>3464/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>231/NAG/KK/VIII/2026</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>CBD 2026 08 898 01 25179</t>
-  </si>
-  <si>
-    <t>002923/BPJ/CB/2026</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>032304</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
+    <t>740</t>
+  </si>
+  <si>
+    <t>5772387062</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>OFC/OUT/0926/01507</t>
+  </si>
+  <si>
+    <t>0218/E/NAK/0926</t>
+  </si>
+  <si>
+    <t>5772394283</t>
+  </si>
+  <si>
+    <t>OFC/OUT/0926/01505</t>
+  </si>
+  <si>
+    <t>0211.E.NAG.0926</t>
+  </si>
+  <si>
+    <t>0212/E/NAG/0926</t>
+  </si>
+  <si>
+    <t>030706</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>026437</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>020793</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
   </si>
   <si>
     <t>KODE CARA ANGKUT</t>
@@ -608,6 +735,33 @@
     <t>CARA PENGANGKUTAN LAINNYA</t>
   </si>
   <si>
+    <t>K - MILE AIR</t>
+  </si>
+  <si>
+    <t>8K0801</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>JOSEPHINE MAERSK</t>
+  </si>
+  <si>
+    <t>638 N</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>MSC SHAULA</t>
+  </si>
+  <si>
+    <t>HW634A</t>
+  </si>
+  <si>
+    <t>LR</t>
+  </si>
+  <si>
     <t>KODE KEMASAN</t>
   </si>
   <si>
@@ -623,6 +777,12 @@
     <t>PK</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
     <t>NOMOR KONTINER</t>
   </si>
   <si>
@@ -635,6 +795,12 @@
     <t>KODE TIPE KONTAINER</t>
   </si>
   <si>
+    <t>MSNU3559121</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>SERI BARANG</t>
   </si>
   <si>
@@ -794,28 +960,145 @@
     <t>STATEMENT PERBEDAAN HARGA</t>
   </si>
   <si>
-    <t>62101019</t>
-  </si>
-  <si>
-    <t>2910</t>
-  </si>
-  <si>
-    <t>PANEL UNTUK DI EMBROIDERRY (KNITTED FABRIC 100% POLYESTER)</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>60063210</t>
+  </si>
+  <si>
+    <t>FABRIC SAMPLE 
+FABRIC 90% MODAL 10% SPANDEX SINGLE JERSEY</t>
+  </si>
+  <si>
+    <t>YRD</t>
+  </si>
+  <si>
+    <t>3204</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>54082200</t>
+  </si>
+  <si>
+    <t>FABRIC SAMPLE 
+SINGLE JERSEY 54% COTTON 36% MODAL 10% SPANDEX</t>
+  </si>
+  <si>
+    <t>61034200</t>
+  </si>
+  <si>
+    <t>BYN/0626/003</t>
+  </si>
+  <si>
+    <t>LONG PANTS
+SPACEDYE FOLDOVER PANT
+PO NO : 2100221058
+STYLE : SD1367
+COLOUR : SILVER MIST</t>
   </si>
   <si>
     <t>PCE</t>
   </si>
   <si>
-    <t>TW</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>PANEL UNTUK DI PRINTING (88% NYLON 12% ELASTANE POWER MESH)</t>
+    <t>61103000</t>
+  </si>
+  <si>
+    <t>BYN/0526/032</t>
+  </si>
+  <si>
+    <t>HALF ZIPPER
+SPACEDYE TERRAIN MENS QUARTER ZIP PULLOVER
+PO NO : 2100221064
+STYLE : SD7971D
+COLOUR : MOUNTAIN GREEN / TRUE WHITE</t>
+  </si>
+  <si>
+    <t>LONG PANTS
+SPACEDYE FOLDOVER PANT
+PO NO : 2100221056
+STYLE : SD1367
+COLOUR : BLUE TUNDRA HEATHER</t>
+  </si>
+  <si>
+    <t>BYN/0626/002</t>
+  </si>
+  <si>
+    <t>HALF ZIPPER
+COURSE CONTRAST HALF ZIP PULLOVER
+PO NO : 2100218970
+STYLE : NN7951
+COLOUR : MOUNTAIN GREEN / TRUE WHITE</t>
+  </si>
+  <si>
+    <t>HALF ZIPPER
+SPACEDYE TERRAIN MENS QUARTER ZIP PULLOVER
+PO NO : 2100221063
+STYLE : SD7971D
+COLOUR : BLUE TUNDRA / TRUE WHITE</t>
+  </si>
+  <si>
+    <t>HALF ZIPPER
+COURSE CONTRAST HALF ZIP PULLOVER
+PO NO : 2100218971
+STYLE : NN7951
+COLOUR : MOUNTAIN GREEN / TRUE WHITE</t>
+  </si>
+  <si>
+    <t>LONG PANTS
+SPACEDYE FOLDOVER PANT
+PO NO : 2100221057
+STYLE : SD1367
+COLOUR :  DARKEST NIGHT</t>
+  </si>
+  <si>
+    <t>BYN/0526/028</t>
+  </si>
+  <si>
+    <t>LONG PANTS
+STRETCH WOVEN WIDE LEG 29'' PANT
+PO NO : 2100221066
+STYLE : NN1263S
+COLOUR : BLUE TUNDRA</t>
+  </si>
+  <si>
+    <t>LONG PANTS
+STRETCH WOVEN WIDE LEG 29'' PANT
+PO NO : 2100221065
+STYLE : NN1263
+COLOUR : BLUE TUNDRA</t>
+  </si>
+  <si>
+    <t>61091010</t>
+  </si>
+  <si>
+    <t>IMS/0726/012</t>
+  </si>
+  <si>
+    <t>T-SHIRT (SPROUTS MENS TEES 00167)
+PO :  2006838IN 
+COLOR :  HEATHEREDFOREST GREEN</t>
+  </si>
+  <si>
+    <t>3XL/5XL</t>
+  </si>
+  <si>
+    <t>IMS/0726/013</t>
+  </si>
+  <si>
+    <t>T-SHIRT (SPROUTS MENS TEES 00167)
+PO :  2009823IN
+COLOR :  HEATHEREDFOREST GREEN</t>
+  </si>
+  <si>
+    <t>S/M</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>S/M/L/XL/2XL</t>
+  </si>
+  <si>
+    <t>3XL/4XL/5XL/6XL</t>
   </si>
   <si>
     <t>KODE PUNGUTAN</t>
@@ -875,39 +1158,6 @@
     <t>VALUTA</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>60063290</t>
-  </si>
-  <si>
-    <t>KNITTED FABRIC 100% POLYESTER (55892 YRD)</t>
-  </si>
-  <si>
-    <t>KGM</t>
-  </si>
-  <si>
-    <t>07-28-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>000023NIW34520260728000219</t>
-  </si>
-  <si>
-    <t>60041010</t>
-  </si>
-  <si>
-    <t>88% NYLON 12% ELASTANE POWER MESH (1699 YRD)</t>
-  </si>
-  <si>
-    <t>08-13-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>000023NIW34520260810000227</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>KODE_ASAL_BAHAN_BAKU</t>
   </si>
   <si>
@@ -935,24 +1185,12 @@
     <t>TANGGAL BPJ</t>
   </si>
   <si>
-    <t>08-27-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>JAMKRIDA JAKARTA</t>
-  </si>
-  <si>
-    <t>11-23-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>08-24-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>11-18-2026 00:00:00</t>
-  </si>
-  <si>
     <t>NAMA</t>
   </si>
   <si>
+    <t>BANK BCA</t>
+  </si>
+  <si>
     <t>JENIS NILAI</t>
   </si>
   <si>
@@ -1019,13 +1257,19 @@
     <t>TANGGAL RESPON</t>
   </si>
   <si>
-    <t>26108</t>
-  </si>
-  <si>
-    <t>020770/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>020774/KBC.0903/2026</t>
+    <t>3015</t>
+  </si>
+  <si>
+    <t>462383/KPU.3/2026</t>
+  </si>
+  <si>
+    <t>462721/KPU.3/2026</t>
+  </si>
+  <si>
+    <t>576394/PM/KPU.1/2026</t>
+  </si>
+  <si>
+    <t>575565/PM/KPU.1/2026</t>
   </si>
 </sst>
 </file>
@@ -1151,14 +1395,16 @@
     <col min="65" max="65" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="66" max="66" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="69" max="69" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="78" max="78" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="79" max="79" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="80" max="80" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="81" max="81" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="83" max="83" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="84" max="84" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="85" max="85" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1519,23 +1765,86 @@
       <c r="C2" t="s">
         <v>106</v>
       </c>
-      <c r="N2" t="s">
+      <c r="E2" t="s">
         <v>107</v>
       </c>
+      <c r="G2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P2" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>110</v>
+      </c>
+      <c r="W2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>123</v>
+      </c>
       <c r="BK2" t="n">
         <v>0.0</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN2" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO2" t="n">
         <v>0.0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0</v>
+        <v>0.17</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="BR2" t="n">
         <v>0.0</v>
@@ -1547,13 +1856,13 @@
         <v>0.0</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.912939436E7</v>
+        <v>0.0</v>
       </c>
       <c r="BV2" t="n">
         <v>0.0</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.0</v>
+        <v>17714.0</v>
       </c>
       <c r="BY2" t="n">
         <v>0.0</v>
@@ -1562,42 +1871,54 @@
         <v>0.0</v>
       </c>
       <c r="CB2" t="n">
-        <v>670.5</v>
+        <v>0.55</v>
       </c>
       <c r="CC2" t="n">
-        <v>670.13</v>
+        <v>0.5</v>
       </c>
       <c r="CD2" t="n">
         <v>0.0</v>
       </c>
       <c r="CE2" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB2" t="s">
         <v>108</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
         <v>105</v>
@@ -1605,23 +1926,86 @@
       <c r="C3" t="s">
         <v>106</v>
       </c>
-      <c r="N3" t="s">
+      <c r="E3" t="s">
         <v>107</v>
       </c>
+      <c r="G3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>123</v>
+      </c>
       <c r="BK3" t="n">
         <v>0.0</v>
       </c>
       <c r="BL3" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO3" t="n">
         <v>0.0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="BR3" t="n">
         <v>0.0</v>
@@ -1633,13 +2017,13 @@
         <v>0.0</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.026117357E7</v>
+        <v>0.0</v>
       </c>
       <c r="BV3" t="n">
         <v>0.0</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.0</v>
+        <v>17714.0</v>
       </c>
       <c r="BY3" t="n">
         <v>0.0</v>
@@ -1648,37 +2032,347 @@
         <v>0.0</v>
       </c>
       <c r="CB3" t="n">
-        <v>45.0</v>
+        <v>0.5</v>
       </c>
       <c r="CC3" t="n">
-        <v>44.81</v>
+        <v>0.1</v>
       </c>
       <c r="CD3" t="n">
         <v>0.0</v>
       </c>
       <c r="CE3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB3" t="s">
         <v>108</v>
       </c>
-      <c r="CF3" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" t="s">
+        <v>108</v>
+      </c>
+      <c r="P4" t="s">
         <v>109</v>
       </c>
-      <c r="CG3" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH3" t="s">
+      <c r="Q4" t="s">
+        <v>137</v>
+      </c>
+      <c r="W4" t="s">
         <v>111</v>
       </c>
-      <c r="CI3" t="s">
+      <c r="AA4" t="s">
         <v>112</v>
       </c>
-      <c r="CP3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CQ3" t="s">
+      <c r="AH4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>23746.25</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1346.41</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>23746.25</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>3072.074</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>2885.714</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>136</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>141</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" t="s">
+        <v>108</v>
+      </c>
+      <c r="P5" t="s">
         <v>109</v>
       </c>
-      <c r="CT3" t="n">
-        <v>0.0</v>
+      <c r="Q5" t="s">
+        <v>137</v>
+      </c>
+      <c r="W5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>143</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>11891.88</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>60321.3</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>3792.56</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>3351.3</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>144</v>
+      </c>
+      <c r="CO5" t="s">
+        <v>136</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>145</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB5" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1699,7 +2393,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1710,35 +2404,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>272</v>
+        <v>349</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -1769,10 +2441,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>273</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -1802,13 +2474,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>274</v>
+        <v>351</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -1842,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>275</v>
+        <v>352</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -1857,7 +2529,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -1878,13 +2550,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="45.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1894,10 +2564,9 @@
     <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1918,64 +2587,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>354</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>355</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -1990,218 +2659,52 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>279</v>
+        <v>356</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" t="s">
-        <v>256</v>
-      </c>
-      <c r="G2" t="s">
-        <v>282</v>
-      </c>
-      <c r="H2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I2" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K2" t="s">
-        <v>256</v>
-      </c>
-      <c r="L2" t="s">
-        <v>283</v>
-      </c>
-      <c r="M2" t="n">
-        <v>670.13</v>
-      </c>
-      <c r="P2" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>106</v>
-      </c>
-      <c r="R2" t="s">
-        <v>174</v>
-      </c>
-      <c r="S2" t="s">
-        <v>284</v>
-      </c>
-      <c r="T2" t="s">
-        <v>285</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>14572.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.912939436E7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7.912939436E7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7.912939436E7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E3" t="s">
-        <v>286</v>
-      </c>
-      <c r="F3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G3" t="s">
-        <v>287</v>
-      </c>
-      <c r="H3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I3" t="s">
-        <v>256</v>
-      </c>
-      <c r="J3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K3" t="s">
-        <v>256</v>
-      </c>
-      <c r="L3" t="s">
-        <v>283</v>
-      </c>
-      <c r="M3" t="n">
-        <v>44.81</v>
-      </c>
-      <c r="P3" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>106</v>
-      </c>
-      <c r="R3" t="s">
-        <v>182</v>
-      </c>
-      <c r="S3" t="s">
-        <v>288</v>
-      </c>
-      <c r="T3" t="s">
-        <v>289</v>
-      </c>
-      <c r="U3" t="n">
-        <v>15</v>
-      </c>
-      <c r="V3" t="n">
-        <v>485.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.026117357E7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.026117357E7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.026117357E7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -2222,7 +2725,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2253,384 +2756,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>264</v>
+        <v>341</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>265</v>
+        <v>342</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>266</v>
+        <v>343</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>267</v>
+        <v>344</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>268</v>
+        <v>345</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23880.0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.60027044E7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>283</v>
-      </c>
-      <c r="N2" t="n">
-        <v>670.13</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G3" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.177016587E7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M3" t="s">
-        <v>283</v>
-      </c>
-      <c r="N3" t="n">
-        <v>670.13</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>280</v>
-      </c>
-      <c r="E4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" t="s">
-        <v>290</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2675037.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>283</v>
-      </c>
-      <c r="N4" t="n">
-        <v>670.13</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>280</v>
-      </c>
-      <c r="E5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I5" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.186940915E7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M5" t="s">
-        <v>283</v>
-      </c>
-      <c r="N5" t="n">
-        <v>670.13</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" t="s">
-        <v>290</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I6" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1026117.36</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>283</v>
-      </c>
-      <c r="N6" t="n">
-        <v>44.81</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" t="s">
-        <v>290</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H7" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>282182.27</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>283</v>
-      </c>
-      <c r="N7" t="n">
-        <v>44.81</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>280</v>
-      </c>
-      <c r="E8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" t="s">
-        <v>290</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I8" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1241602.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M8" t="s">
-        <v>283</v>
-      </c>
-      <c r="N8" t="n">
-        <v>44.81</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2664,19 +2859,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>354</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>291</v>
+        <v>357</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>349</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -2697,7 +2892,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2709,114 +2904,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2675037.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.6002704E7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.1770165E7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.1869409E7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1241602.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1026117.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" t="n">
-        <v>282182.0</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2837,16 +2934,16 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2857,86 +2954,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>292</v>
+        <v>358</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>293</v>
+        <v>359</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>294</v>
+        <v>360</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>296</v>
+        <v>362</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>297</v>
+        <v>363</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>298</v>
+        <v>364</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.61927E8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H2" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" t="s">
-        <v>170</v>
-      </c>
-      <c r="J2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2.1907E7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>301</v>
-      </c>
-      <c r="H3" t="s">
-        <v>304</v>
-      </c>
-      <c r="I3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -2957,7 +2996,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2965,13 +3005,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>274</v>
+        <v>351</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -2996,8 +3092,8 @@
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="107.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="55.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="156.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3014,49 +3110,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2">
@@ -3064,31 +3160,31 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H2" t="s">
-        <v>145</v>
-      </c>
-      <c r="K2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L2" t="s">
-        <v>147</v>
+        <v>168</v>
+      </c>
+      <c r="I2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J2" t="s">
+        <v>170</v>
+      </c>
+      <c r="O2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="3">
@@ -3096,28 +3192,19 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J3" t="s">
-        <v>152</v>
+        <v>172</v>
+      </c>
+      <c r="M3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -3125,118 +3212,428 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="F4" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I4" t="s">
-        <v>151</v>
-      </c>
-      <c r="J4" t="s">
-        <v>152</v>
+        <v>172</v>
+      </c>
+      <c r="M4" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="G5" t="s">
-        <v>156</v>
-      </c>
-      <c r="I5" t="s">
-        <v>151</v>
+        <v>176</v>
+      </c>
+      <c r="H5" t="s">
+        <v>177</v>
       </c>
       <c r="J5" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
-      </c>
-      <c r="I6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J6" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I8" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" t="s">
+        <v>170</v>
+      </c>
+      <c r="O8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" t="s">
+        <v>182</v>
+      </c>
+      <c r="M9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" t="s">
+        <v>182</v>
+      </c>
+      <c r="M10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" t="s">
+        <v>177</v>
+      </c>
+      <c r="J11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G12" t="s">
+        <v>185</v>
+      </c>
+      <c r="I12" t="s">
+        <v>169</v>
+      </c>
+      <c r="J12" t="s">
+        <v>170</v>
+      </c>
+      <c r="O12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F13" t="s">
+        <v>188</v>
+      </c>
+      <c r="G13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" t="s">
+        <v>177</v>
+      </c>
+      <c r="J14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F15" t="s">
+        <v>190</v>
+      </c>
+      <c r="G15" t="s">
+        <v>191</v>
+      </c>
+      <c r="M15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16" t="s">
+        <v>192</v>
+      </c>
+      <c r="M16" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
         <v>142</v>
       </c>
-      <c r="F7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H7" t="s">
-        <v>145</v>
-      </c>
-      <c r="K7" t="s">
-        <v>146</v>
-      </c>
-      <c r="L7" t="s">
-        <v>147</v>
+      <c r="B17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G17" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" t="s">
+        <v>177</v>
+      </c>
+      <c r="J17" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" t="s">
+        <v>194</v>
+      </c>
+      <c r="G18" t="s">
+        <v>195</v>
+      </c>
+      <c r="M18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19" t="s">
+        <v>194</v>
+      </c>
+      <c r="G19" t="s">
+        <v>195</v>
+      </c>
+      <c r="M19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" t="s">
+        <v>165</v>
+      </c>
+      <c r="I21" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3259,12 +3656,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>323</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -3296,27 +3693,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>325</v>
+        <v>387</v>
       </c>
       <c r="C1" t="s">
-        <v>326</v>
+        <v>388</v>
       </c>
       <c r="D1" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="C2" t="s">
-        <v>329</v>
+        <v>391</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -3324,13 +3721,41 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>392</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D5" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3353,7 +3778,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="29.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3364,22 +3789,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2">
@@ -3390,13 +3815,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="E2" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3">
@@ -3407,13 +3832,13 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -3424,13 +3849,13 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -3441,13 +3866,13 @@
         <v>4.0</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="E5" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6">
@@ -3458,132 +3883,251 @@
         <v>5.0</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="B7" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D7" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="E7" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B8" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="D8" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="E8" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B9" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B10" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B11" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B12" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D14" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18" t="s">
+        <v>217</v>
+      </c>
+      <c r="E18" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" t="n">
         <v>6.0</v>
       </c>
-      <c r="C13" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E13" t="s">
-        <v>183</v>
+      <c r="C20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" t="s">
+        <v>221</v>
+      </c>
+      <c r="E20" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3606,7 +4150,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3619,28 +4163,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2">
@@ -3651,18 +4195,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>186</v>
+      </c>
+      <c r="D2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>186</v>
+      </c>
+      <c r="D3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F5" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3694,19 +4296,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2">
@@ -3717,24 +4319,64 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" t="n">
+        <v>202</v>
+      </c>
+      <c r="E4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" t="n">
+        <v>330</v>
+      </c>
+      <c r="E5" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3755,7 +4397,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3768,22 +4410,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>194</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3825,61 +4487,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>307</v>
+        <v>369</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>308</v>
+        <v>370</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>309</v>
+        <v>371</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>310</v>
+        <v>372</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>373</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>313</v>
+        <v>375</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>315</v>
+        <v>377</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>317</v>
+        <v>379</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>318</v>
+        <v>380</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>319</v>
+        <v>381</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>320</v>
+        <v>382</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>321</v>
+        <v>383</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>322</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -3903,8 +4565,10 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="60.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="127.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3916,11 +4580,11 @@
     <col min="17" max="17" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3967,58 +4631,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -4030,19 +4694,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -4057,25 +4721,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -4084,94 +4748,94 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>233</v>
+        <v>285</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>250</v>
+        <v>302</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2">
@@ -4182,65 +4846,68 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>253</v>
+        <v>305</v>
       </c>
       <c r="D2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E2" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="F2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="G2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="H2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="J2" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="K2" t="n">
-        <v>8703.0</v>
+        <v>2.0</v>
       </c>
       <c r="L2" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="M2" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="T2" t="n">
-        <v>670.13</v>
+        <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.912939436E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.912939436E7</v>
+        <v>0.0</v>
       </c>
       <c r="AB2" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AK2" t="n">
         <v>0.0</v>
       </c>
@@ -4250,74 +4917,77 @@
       <c r="AN2" t="n">
         <v>0.0</v>
       </c>
-      <c r="AR2" t="s">
-        <v>140</v>
+      <c r="AS2" t="s">
+        <v>308</v>
       </c>
       <c r="AY2" t="s">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO2" t="s">
+        <v>108</v>
+      </c>
       <c r="BR2" t="s">
-        <v>259</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="D3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E3" t="s">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="F3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="G3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="H3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="J3" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="K3" t="n">
-        <v>582.0</v>
+        <v>0.25</v>
       </c>
       <c r="L3" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="M3" t="n">
         <v>1.0</v>
       </c>
       <c r="T3" t="n">
-        <v>44.81</v>
+        <v>0.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.026117357E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.026117357E7</v>
+        <v>0.0</v>
       </c>
       <c r="AB3" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.0</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AF3" t="n">
         <v>0.0</v>
       </c>
@@ -4330,6 +5000,9 @@
       <c r="AI3" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>4.0</v>
+      </c>
       <c r="AK3" t="n">
         <v>0.0</v>
       </c>
@@ -4339,17 +5012,1350 @@
       <c r="AN3" t="n">
         <v>0.0</v>
       </c>
-      <c r="AR3" t="s">
-        <v>140</v>
+      <c r="AS3" t="s">
+        <v>308</v>
       </c>
       <c r="AY3" t="s">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO3" t="s">
+        <v>108</v>
+      </c>
       <c r="BR3" t="s">
-        <v>259</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J4" t="s">
+        <v>315</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1092.0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>245</v>
+      </c>
+      <c r="M4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>467.559</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2129.4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D5" t="s">
+        <v>317</v>
+      </c>
+      <c r="E5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J5" t="s">
+        <v>315</v>
+      </c>
+      <c r="K5" t="n">
+        <v>955.0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>201.506</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2435.25</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E6" t="s">
+        <v>319</v>
+      </c>
+      <c r="F6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I6" t="s">
+        <v>244</v>
+      </c>
+      <c r="J6" t="s">
+        <v>315</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1191.0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>245</v>
+      </c>
+      <c r="M6" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>510.56</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2322.45</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F7" t="s">
+        <v>244</v>
+      </c>
+      <c r="G7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I7" t="s">
+        <v>244</v>
+      </c>
+      <c r="J7" t="s">
+        <v>315</v>
+      </c>
+      <c r="K7" t="n">
+        <v>626.0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>245</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>129.15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3230.16</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E8" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" t="s">
+        <v>244</v>
+      </c>
+      <c r="G8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H8" t="s">
+        <v>244</v>
+      </c>
+      <c r="I8" t="s">
+        <v>244</v>
+      </c>
+      <c r="J8" t="s">
+        <v>315</v>
+      </c>
+      <c r="K8" t="n">
+        <v>547.0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>245</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>114.628</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1394.85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" t="s">
+        <v>320</v>
+      </c>
+      <c r="E9" t="s">
+        <v>323</v>
+      </c>
+      <c r="F9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" t="s">
+        <v>244</v>
+      </c>
+      <c r="H9" t="s">
+        <v>244</v>
+      </c>
+      <c r="I9" t="s">
+        <v>244</v>
+      </c>
+      <c r="J9" t="s">
+        <v>315</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1076.0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>245</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>222.841</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5552.16</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D10" t="s">
+        <v>313</v>
+      </c>
+      <c r="E10" t="s">
+        <v>324</v>
+      </c>
+      <c r="F10" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" t="s">
+        <v>244</v>
+      </c>
+      <c r="H10" t="s">
+        <v>244</v>
+      </c>
+      <c r="I10" t="s">
+        <v>244</v>
+      </c>
+      <c r="J10" t="s">
+        <v>315</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2481.0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>245</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1064.727</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4837.95</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D11" t="s">
+        <v>325</v>
+      </c>
+      <c r="E11" t="s">
+        <v>326</v>
+      </c>
+      <c r="F11" t="s">
+        <v>244</v>
+      </c>
+      <c r="G11" t="s">
+        <v>244</v>
+      </c>
+      <c r="H11" t="s">
+        <v>244</v>
+      </c>
+      <c r="I11" t="s">
+        <v>244</v>
+      </c>
+      <c r="J11" t="s">
+        <v>315</v>
+      </c>
+      <c r="K11" t="n">
+        <v>334.0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>245</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>86.201</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>848.36</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>312</v>
+      </c>
+      <c r="D12" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" t="s">
+        <v>327</v>
+      </c>
+      <c r="F12" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" t="s">
+        <v>244</v>
+      </c>
+      <c r="H12" t="s">
+        <v>244</v>
+      </c>
+      <c r="I12" t="s">
+        <v>244</v>
+      </c>
+      <c r="J12" t="s">
+        <v>315</v>
+      </c>
+      <c r="K12" t="n">
+        <v>333.0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>245</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>88.542</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>995.67</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO12" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>328</v>
+      </c>
+      <c r="D13" t="s">
+        <v>329</v>
+      </c>
+      <c r="E13" t="s">
+        <v>330</v>
+      </c>
+      <c r="F13" t="s">
+        <v>244</v>
+      </c>
+      <c r="G13" t="s">
+        <v>244</v>
+      </c>
+      <c r="H13" t="s">
+        <v>331</v>
+      </c>
+      <c r="I13" t="s">
+        <v>244</v>
+      </c>
+      <c r="J13" t="s">
+        <v>315</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>245</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO13" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>328</v>
+      </c>
+      <c r="D14" t="s">
+        <v>332</v>
+      </c>
+      <c r="E14" t="s">
+        <v>333</v>
+      </c>
+      <c r="F14" t="s">
+        <v>244</v>
+      </c>
+      <c r="G14" t="s">
+        <v>244</v>
+      </c>
+      <c r="H14" t="s">
+        <v>334</v>
+      </c>
+      <c r="I14" t="s">
+        <v>244</v>
+      </c>
+      <c r="J14" t="s">
+        <v>335</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2283.0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>245</v>
+      </c>
+      <c r="M14" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1085.88</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>20547.0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>328</v>
+      </c>
+      <c r="D15" t="s">
+        <v>329</v>
+      </c>
+      <c r="E15" t="s">
+        <v>330</v>
+      </c>
+      <c r="F15" t="s">
+        <v>244</v>
+      </c>
+      <c r="G15" t="s">
+        <v>244</v>
+      </c>
+      <c r="H15" t="s">
+        <v>336</v>
+      </c>
+      <c r="I15" t="s">
+        <v>244</v>
+      </c>
+      <c r="J15" t="s">
+        <v>335</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4093.0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>245</v>
+      </c>
+      <c r="M15" t="n">
+        <v>203.0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2101.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>36837.0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO15" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D16" t="s">
+        <v>329</v>
+      </c>
+      <c r="E16" t="s">
+        <v>330</v>
+      </c>
+      <c r="F16" t="s">
+        <v>244</v>
+      </c>
+      <c r="G16" t="s">
+        <v>244</v>
+      </c>
+      <c r="H16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I16" t="s">
+        <v>244</v>
+      </c>
+      <c r="J16" t="s">
+        <v>335</v>
+      </c>
+      <c r="K16" t="n">
+        <v>231.0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>245</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2564.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO16" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" t="s">
+        <v>329</v>
+      </c>
+      <c r="E17" t="s">
+        <v>330</v>
+      </c>
+      <c r="F17" t="s">
+        <v>336</v>
+      </c>
+      <c r="G17" t="s">
+        <v>244</v>
+      </c>
+      <c r="H17" t="s">
+        <v>244</v>
+      </c>
+      <c r="I17" t="s">
+        <v>244</v>
+      </c>
+      <c r="J17" t="s">
+        <v>315</v>
+      </c>
+      <c r="K17" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="L17" t="s">
+        <v>245</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>17714.0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>351.0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>308</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO17" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR17" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4395,58 +6401,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>264</v>
+        <v>341</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>265</v>
+        <v>342</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>266</v>
+        <v>343</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>267</v>
+        <v>344</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>268</v>
+        <v>345</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
